--- a/results/04_final_refined_daily_hydroclimate_data/905/Daily_temperature_and_precipitation_station_905.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/905/Daily_temperature_and_precipitation_station_905.xlsx
@@ -510,17 +510,14 @@
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>28.4</v>
-      </c>
       <c r="E2">
         <v>15.8</v>
       </c>
-      <c r="F2">
-        <v>22.1</v>
-      </c>
-      <c r="I2">
-        <v>23.7</v>
+      <c r="H2">
+        <v>17.9</v>
+      </c>
+      <c r="J2">
+        <v>20.3</v>
       </c>
       <c r="K2">
         <v>16.8</v>
@@ -528,6 +525,9 @@
       <c r="L2">
         <v>21.8</v>
       </c>
+      <c r="M2">
+        <v>18.7</v>
+      </c>
       <c r="R2" s="2">
         <v>26969</v>
       </c>
@@ -551,8 +551,11 @@
       <c r="E3">
         <v>16.9</v>
       </c>
-      <c r="I3">
-        <v>24.8</v>
+      <c r="H3">
+        <v>18.3</v>
+      </c>
+      <c r="J3">
+        <v>18</v>
       </c>
       <c r="K3">
         <v>17.6</v>
@@ -560,6 +563,9 @@
       <c r="L3">
         <v>21.3</v>
       </c>
+      <c r="M3">
+        <v>17.2</v>
+      </c>
       <c r="R3" s="2">
         <v>26970</v>
       </c>
@@ -589,15 +595,24 @@
       <c r="F4">
         <v>22.9</v>
       </c>
+      <c r="H4">
+        <v>17.2</v>
+      </c>
       <c r="I4">
         <v>26.8</v>
       </c>
+      <c r="J4">
+        <v>20.2</v>
+      </c>
       <c r="K4">
-        <v>16.4</v>
+        <v>16</v>
       </c>
       <c r="L4">
         <v>20.6</v>
       </c>
+      <c r="M4">
+        <v>19.2</v>
+      </c>
       <c r="R4" s="2">
         <v>26971</v>
       </c>
@@ -622,19 +637,25 @@
         <v>28.2</v>
       </c>
       <c r="E5">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="F5">
-        <v>22.1</v>
-      </c>
-      <c r="I5">
-        <v>27.3</v>
+        <v>22.2</v>
+      </c>
+      <c r="H5">
+        <v>19</v>
+      </c>
+      <c r="J5">
+        <v>20.8</v>
       </c>
       <c r="K5">
         <v>17.9</v>
       </c>
       <c r="L5">
-        <v>21</v>
+        <v>22.7</v>
+      </c>
+      <c r="M5">
+        <v>19.6</v>
       </c>
       <c r="R5" s="2">
         <v>26972</v>
@@ -665,6 +686,9 @@
       <c r="F6">
         <v>22.7</v>
       </c>
+      <c r="H6">
+        <v>17</v>
+      </c>
       <c r="I6">
         <v>24.5</v>
       </c>
@@ -678,7 +702,7 @@
         <v>22.2</v>
       </c>
       <c r="M6">
-        <v>17.3</v>
+        <v>18</v>
       </c>
       <c r="R6" s="2">
         <v>26973</v>
@@ -700,14 +724,23 @@
       <c r="C7">
         <v>6</v>
       </c>
-      <c r="H7">
-        <v>17.2</v>
+      <c r="D7">
+        <v>26.5</v>
+      </c>
+      <c r="E7">
+        <v>16.8</v>
+      </c>
+      <c r="F7">
+        <v>21.7</v>
       </c>
       <c r="I7">
         <v>26</v>
       </c>
       <c r="J7">
-        <v>21.8</v>
+        <v>21.7</v>
+      </c>
+      <c r="K7">
+        <v>17</v>
       </c>
       <c r="L7">
         <v>19.7</v>
@@ -733,16 +766,13 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
       <c r="E8">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="F8">
-        <v>22.4</v>
-      </c>
-      <c r="H8">
-        <v>18.4</v>
+        <v>22.3</v>
       </c>
       <c r="I8">
         <v>20.3</v>
@@ -750,6 +780,15 @@
       <c r="J8">
         <v>21.5</v>
       </c>
+      <c r="K8">
+        <v>17.6</v>
+      </c>
+      <c r="L8">
+        <v>19.5</v>
+      </c>
+      <c r="M8">
+        <v>19.7</v>
+      </c>
       <c r="R8" s="2">
         <v>26975</v>
       </c>
@@ -774,20 +813,23 @@
         <v>27.5</v>
       </c>
       <c r="E9">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="F9">
         <v>22.3</v>
       </c>
-      <c r="H9">
-        <v>17.7</v>
-      </c>
       <c r="I9">
         <v>24.4</v>
       </c>
       <c r="J9">
         <v>19.8</v>
       </c>
+      <c r="K9">
+        <v>16.9</v>
+      </c>
+      <c r="L9">
+        <v>21.4</v>
+      </c>
       <c r="R9" s="2">
         <v>26976</v>
       </c>
@@ -817,15 +859,18 @@
       <c r="F10">
         <v>21.1</v>
       </c>
-      <c r="H10">
-        <v>18.3</v>
-      </c>
       <c r="I10">
         <v>21</v>
       </c>
       <c r="J10">
         <v>19.7</v>
       </c>
+      <c r="K10">
+        <v>17.2</v>
+      </c>
+      <c r="L10">
+        <v>20.3</v>
+      </c>
       <c r="M10">
         <v>19.4</v>
       </c>
@@ -858,17 +903,17 @@
       <c r="F11">
         <v>22.5</v>
       </c>
-      <c r="H11">
-        <v>17.2</v>
-      </c>
       <c r="I11">
-        <v>27.6</v>
+        <v>28.6</v>
       </c>
       <c r="J11">
         <v>19.2</v>
       </c>
       <c r="K11">
-        <v>16.3</v>
+        <v>16.6</v>
+      </c>
+      <c r="L11">
+        <v>21.4</v>
       </c>
       <c r="R11" s="2">
         <v>26978</v>
@@ -899,12 +944,6 @@
       <c r="F12">
         <v>22.4</v>
       </c>
-      <c r="J12">
-        <v>20.9</v>
-      </c>
-      <c r="M12">
-        <v>18.9</v>
-      </c>
       <c r="R12" s="2">
         <v>26979</v>
       </c>
@@ -934,12 +973,6 @@
       <c r="F13">
         <v>21.8</v>
       </c>
-      <c r="J13">
-        <v>23.4</v>
-      </c>
-      <c r="M13">
-        <v>19.9</v>
-      </c>
       <c r="R13" s="2">
         <v>26980</v>
       </c>
@@ -1030,24 +1063,12 @@
       <c r="C16">
         <v>15</v>
       </c>
-      <c r="D16">
-        <v>27.6</v>
-      </c>
       <c r="E16">
         <v>17</v>
       </c>
-      <c r="F16">
-        <v>22.3</v>
-      </c>
-      <c r="H16">
-        <v>19.2</v>
-      </c>
       <c r="J16">
         <v>23.1</v>
       </c>
-      <c r="K16">
-        <v>18.7</v>
-      </c>
       <c r="M16">
         <v>17.2</v>
       </c>
@@ -1086,9 +1107,6 @@
       <c r="K17">
         <v>18.2</v>
       </c>
-      <c r="L17">
-        <v>19.1</v>
-      </c>
       <c r="R17" s="2">
         <v>26984</v>
       </c>
@@ -1121,12 +1139,18 @@
       <c r="I18">
         <v>23.7</v>
       </c>
+      <c r="J18">
+        <v>20.6</v>
+      </c>
       <c r="K18">
         <v>16.7</v>
       </c>
       <c r="L18">
         <v>20.8</v>
       </c>
+      <c r="M18">
+        <v>19.3</v>
+      </c>
       <c r="R18" s="2">
         <v>26985</v>
       </c>
@@ -1148,17 +1172,23 @@
         <v>18</v>
       </c>
       <c r="D19">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="E19">
         <v>16.6</v>
       </c>
       <c r="F19">
-        <v>21.7</v>
+        <v>21.8</v>
+      </c>
+      <c r="I19">
+        <v>25.5</v>
       </c>
       <c r="K19">
         <v>16.1</v>
       </c>
+      <c r="L19">
+        <v>19.5</v>
+      </c>
       <c r="R19" s="2">
         <v>26986</v>
       </c>
@@ -1188,9 +1218,15 @@
       <c r="F20">
         <v>21.9</v>
       </c>
+      <c r="I20">
+        <v>20.8</v>
+      </c>
       <c r="K20">
         <v>15</v>
       </c>
+      <c r="L20">
+        <v>16.2</v>
+      </c>
       <c r="R20" s="2">
         <v>26987</v>
       </c>
@@ -1211,9 +1247,27 @@
       <c r="C21">
         <v>20</v>
       </c>
+      <c r="D21">
+        <v>26.6</v>
+      </c>
+      <c r="E21">
+        <v>16.5</v>
+      </c>
+      <c r="F21">
+        <v>21.2</v>
+      </c>
+      <c r="I21">
+        <v>22</v>
+      </c>
+      <c r="J21">
+        <v>20.2</v>
+      </c>
       <c r="K21">
         <v>15.2</v>
       </c>
+      <c r="M21">
+        <v>18.2</v>
+      </c>
       <c r="R21" s="2">
         <v>26988</v>
       </c>
@@ -1235,13 +1289,16 @@
         <v>21</v>
       </c>
       <c r="D22">
-        <v>26.3</v>
+        <v>26.4</v>
+      </c>
+      <c r="E22">
+        <v>17.1</v>
       </c>
       <c r="F22">
         <v>21.7</v>
       </c>
-      <c r="H22">
-        <v>19.1</v>
+      <c r="L22">
+        <v>18</v>
       </c>
       <c r="R22" s="2">
         <v>26989</v>
@@ -1264,16 +1321,16 @@
         <v>22</v>
       </c>
       <c r="D23">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="E23">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="F23">
         <v>21.8</v>
       </c>
-      <c r="H23">
-        <v>17.1</v>
+      <c r="L23">
+        <v>18.6</v>
       </c>
       <c r="R23" s="2">
         <v>26990</v>
@@ -1304,8 +1361,8 @@
       <c r="F24">
         <v>20.9</v>
       </c>
-      <c r="H24">
-        <v>17.5</v>
+      <c r="L24">
+        <v>20</v>
       </c>
       <c r="R24" s="2">
         <v>26991</v>
@@ -1336,8 +1393,8 @@
       <c r="F25">
         <v>20.7</v>
       </c>
-      <c r="H25">
-        <v>17.6</v>
+      <c r="L25">
+        <v>19.8</v>
       </c>
       <c r="R25" s="2">
         <v>26992</v>
@@ -1360,22 +1417,16 @@
         <v>25</v>
       </c>
       <c r="D26">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="E26">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="F26">
         <v>22.1</v>
       </c>
-      <c r="H26">
-        <v>17.1</v>
-      </c>
-      <c r="I26">
-        <v>26.7</v>
-      </c>
       <c r="L26">
-        <v>18.4</v>
+        <v>20.8</v>
       </c>
       <c r="R26" s="2">
         <v>26993</v>
@@ -1397,6 +1448,18 @@
       <c r="C27">
         <v>26</v>
       </c>
+      <c r="D27">
+        <v>25.4</v>
+      </c>
+      <c r="E27">
+        <v>16</v>
+      </c>
+      <c r="F27">
+        <v>20.7</v>
+      </c>
+      <c r="L27">
+        <v>22.2</v>
+      </c>
       <c r="R27" s="2">
         <v>26994</v>
       </c>
@@ -1418,13 +1481,16 @@
         <v>27</v>
       </c>
       <c r="D28">
-        <v>27.5</v>
+        <v>25.6</v>
       </c>
       <c r="E28">
-        <v>15.6</v>
+        <v>15.8</v>
       </c>
       <c r="F28">
-        <v>21.6</v>
+        <v>20.7</v>
+      </c>
+      <c r="L28">
+        <v>19.5</v>
       </c>
       <c r="R28" s="2">
         <v>26995</v>
@@ -1446,11 +1512,11 @@
       <c r="C29">
         <v>28</v>
       </c>
-      <c r="I29">
-        <v>26</v>
+      <c r="F29">
+        <v>20.5</v>
       </c>
       <c r="L29">
-        <v>17.1</v>
+        <v>20.2</v>
       </c>
       <c r="R29" s="2">
         <v>26996</v>
@@ -1473,14 +1539,17 @@
         <v>29</v>
       </c>
       <c r="D30">
-        <v>27.7</v>
+        <v>28.6</v>
       </c>
       <c r="E30">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="F30">
         <v>22.6</v>
       </c>
+      <c r="L30">
+        <v>19.8</v>
+      </c>
       <c r="R30" s="2">
         <v>26997</v>
       </c>
@@ -1500,6 +1569,18 @@
       </c>
       <c r="C31">
         <v>30</v>
+      </c>
+      <c r="D31">
+        <v>27.5</v>
+      </c>
+      <c r="E31">
+        <v>17.4</v>
+      </c>
+      <c r="F31">
+        <v>22.6</v>
+      </c>
+      <c r="L31">
+        <v>20.2</v>
       </c>
       <c r="R31" s="2">
         <v>26998</v>

--- a/results/04_final_refined_daily_hydroclimate_data/905/Daily_temperature_and_precipitation_station_905.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/905/Daily_temperature_and_precipitation_station_905.xlsx
@@ -510,12 +510,24 @@
       <c r="C2">
         <v>1</v>
       </c>
+      <c r="D2">
+        <v>28.4</v>
+      </c>
       <c r="E2">
-        <v>15.8</v>
+        <v>15.9</v>
+      </c>
+      <c r="F2">
+        <v>22.1</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
       </c>
       <c r="H2">
         <v>17.9</v>
       </c>
+      <c r="I2">
+        <v>23.7</v>
+      </c>
       <c r="J2">
         <v>20.3</v>
       </c>
@@ -548,12 +560,24 @@
       <c r="C3">
         <v>2</v>
       </c>
+      <c r="D3">
+        <v>28.2</v>
+      </c>
       <c r="E3">
         <v>16.9</v>
       </c>
+      <c r="F3">
+        <v>22.6</v>
+      </c>
+      <c r="G3">
+        <v>12.3</v>
+      </c>
       <c r="H3">
         <v>18.3</v>
       </c>
+      <c r="I3">
+        <v>24.8</v>
+      </c>
       <c r="J3">
         <v>18</v>
       </c>
@@ -561,7 +585,7 @@
         <v>17.6</v>
       </c>
       <c r="L3">
-        <v>21.3</v>
+        <v>20</v>
       </c>
       <c r="M3">
         <v>17.2</v>
@@ -595,6 +619,9 @@
       <c r="F4">
         <v>22.9</v>
       </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
       <c r="H4">
         <v>17.2</v>
       </c>
@@ -605,7 +632,7 @@
         <v>20.2</v>
       </c>
       <c r="K4">
-        <v>16</v>
+        <v>16.4</v>
       </c>
       <c r="L4">
         <v>20.6</v>
@@ -642,9 +669,15 @@
       <c r="F5">
         <v>22.2</v>
       </c>
+      <c r="G5">
+        <v>0.2</v>
+      </c>
       <c r="H5">
         <v>19</v>
       </c>
+      <c r="I5">
+        <v>27.3</v>
+      </c>
       <c r="J5">
         <v>20.8</v>
       </c>
@@ -652,7 +685,7 @@
         <v>17.9</v>
       </c>
       <c r="L5">
-        <v>22.7</v>
+        <v>21</v>
       </c>
       <c r="M5">
         <v>19.6</v>
@@ -686,6 +719,9 @@
       <c r="F6">
         <v>22.7</v>
       </c>
+      <c r="G6">
+        <v>4.1</v>
+      </c>
       <c r="H6">
         <v>17</v>
       </c>
@@ -733,6 +769,9 @@
       <c r="F7">
         <v>21.7</v>
       </c>
+      <c r="H7">
+        <v>17.2</v>
+      </c>
       <c r="I7">
         <v>26</v>
       </c>
@@ -745,6 +784,9 @@
       <c r="L7">
         <v>19.7</v>
       </c>
+      <c r="M7">
+        <v>19</v>
+      </c>
       <c r="R7" s="2">
         <v>26974</v>
       </c>
@@ -774,6 +816,9 @@
       <c r="F8">
         <v>22.3</v>
       </c>
+      <c r="H8">
+        <v>18.4</v>
+      </c>
       <c r="I8">
         <v>20.3</v>
       </c>
@@ -818,6 +863,9 @@
       <c r="F9">
         <v>22.3</v>
       </c>
+      <c r="H9">
+        <v>17.7</v>
+      </c>
       <c r="I9">
         <v>24.4</v>
       </c>
@@ -830,6 +878,9 @@
       <c r="L9">
         <v>21.4</v>
       </c>
+      <c r="M9">
+        <v>19.4</v>
+      </c>
       <c r="R9" s="2">
         <v>26976</v>
       </c>
@@ -859,6 +910,9 @@
       <c r="F10">
         <v>21.1</v>
       </c>
+      <c r="H10">
+        <v>18.3</v>
+      </c>
       <c r="I10">
         <v>21</v>
       </c>
@@ -903,8 +957,11 @@
       <c r="F11">
         <v>22.5</v>
       </c>
+      <c r="H11">
+        <v>17.2</v>
+      </c>
       <c r="I11">
-        <v>28.6</v>
+        <v>27.6</v>
       </c>
       <c r="J11">
         <v>19.2</v>
@@ -913,7 +970,10 @@
         <v>16.6</v>
       </c>
       <c r="L11">
-        <v>21.4</v>
+        <v>19</v>
+      </c>
+      <c r="M11">
+        <v>17.7</v>
       </c>
       <c r="R11" s="2">
         <v>26978</v>
@@ -942,7 +1002,19 @@
         <v>17</v>
       </c>
       <c r="F12">
-        <v>22.4</v>
+        <v>22.3</v>
+      </c>
+      <c r="G12">
+        <v>0.8</v>
+      </c>
+      <c r="I12">
+        <v>26.7</v>
+      </c>
+      <c r="K12">
+        <v>16.8</v>
+      </c>
+      <c r="L12">
+        <v>20</v>
       </c>
       <c r="R12" s="2">
         <v>26979</v>
@@ -973,6 +1045,24 @@
       <c r="F13">
         <v>21.8</v>
       </c>
+      <c r="G13">
+        <v>2.3</v>
+      </c>
+      <c r="I13">
+        <v>23.8</v>
+      </c>
+      <c r="J13">
+        <v>23.4</v>
+      </c>
+      <c r="K13">
+        <v>17.4</v>
+      </c>
+      <c r="L13">
+        <v>18.7</v>
+      </c>
+      <c r="M13">
+        <v>18.4</v>
+      </c>
       <c r="R13" s="2">
         <v>26980</v>
       </c>
@@ -1002,9 +1092,21 @@
       <c r="F14">
         <v>22.3</v>
       </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>22.8</v>
+      </c>
       <c r="J14">
         <v>20.9</v>
       </c>
+      <c r="K14">
+        <v>17.9</v>
+      </c>
+      <c r="L14">
+        <v>20.9</v>
+      </c>
       <c r="M14">
         <v>19.9</v>
       </c>
@@ -1037,9 +1139,15 @@
       <c r="F15">
         <v>22.5</v>
       </c>
+      <c r="G15">
+        <v>3.5</v>
+      </c>
       <c r="J15">
         <v>22</v>
       </c>
+      <c r="K15">
+        <v>17.4</v>
+      </c>
       <c r="M15">
         <v>21.6</v>
       </c>
@@ -1063,12 +1171,30 @@
       <c r="C16">
         <v>15</v>
       </c>
+      <c r="D16">
+        <v>27.6</v>
+      </c>
       <c r="E16">
         <v>17</v>
       </c>
+      <c r="F16">
+        <v>22.3</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>25.1</v>
+      </c>
       <c r="J16">
         <v>23.1</v>
       </c>
+      <c r="K16">
+        <v>17.7</v>
+      </c>
+      <c r="L16">
+        <v>20.2</v>
+      </c>
       <c r="M16">
         <v>17.2</v>
       </c>
@@ -1093,13 +1219,16 @@
         <v>16</v>
       </c>
       <c r="D17">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="E17">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="F17">
-        <v>21</v>
+        <v>21.1</v>
+      </c>
+      <c r="G17">
+        <v>3.1</v>
       </c>
       <c r="I17">
         <v>22.2</v>
@@ -1107,6 +1236,9 @@
       <c r="K17">
         <v>18.2</v>
       </c>
+      <c r="L17">
+        <v>19.1</v>
+      </c>
       <c r="R17" s="2">
         <v>26984</v>
       </c>
@@ -1136,6 +1268,9 @@
       <c r="F18">
         <v>20.3</v>
       </c>
+      <c r="G18">
+        <v>2.6</v>
+      </c>
       <c r="I18">
         <v>23.7</v>
       </c>
@@ -1146,7 +1281,7 @@
         <v>16.7</v>
       </c>
       <c r="L18">
-        <v>20.8</v>
+        <v>21.6</v>
       </c>
       <c r="M18">
         <v>19.3</v>
@@ -1172,13 +1307,16 @@
         <v>18</v>
       </c>
       <c r="D19">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="E19">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="F19">
-        <v>21.8</v>
+        <v>21.7</v>
+      </c>
+      <c r="G19">
+        <v>1.2</v>
       </c>
       <c r="I19">
         <v>25.5</v>
@@ -1218,15 +1356,24 @@
       <c r="F20">
         <v>21.9</v>
       </c>
+      <c r="G20">
+        <v>0.1</v>
+      </c>
       <c r="I20">
         <v>20.8</v>
       </c>
+      <c r="J20">
+        <v>19</v>
+      </c>
       <c r="K20">
         <v>15</v>
       </c>
       <c r="L20">
         <v>16.2</v>
       </c>
+      <c r="M20">
+        <v>15.1</v>
+      </c>
       <c r="R20" s="2">
         <v>26987</v>
       </c>
@@ -1248,13 +1395,16 @@
         <v>20</v>
       </c>
       <c r="D21">
-        <v>26.6</v>
+        <v>26.3</v>
       </c>
       <c r="E21">
         <v>16.5</v>
       </c>
       <c r="F21">
-        <v>21.2</v>
+        <v>21.4</v>
+      </c>
+      <c r="G21">
+        <v>0.9</v>
       </c>
       <c r="I21">
         <v>22</v>
@@ -1265,6 +1415,9 @@
       <c r="K21">
         <v>15.2</v>
       </c>
+      <c r="L21">
+        <v>19.7</v>
+      </c>
       <c r="M21">
         <v>18.2</v>
       </c>
@@ -1297,6 +1450,12 @@
       <c r="F22">
         <v>21.7</v>
       </c>
+      <c r="I22">
+        <v>18.3</v>
+      </c>
+      <c r="K22">
+        <v>15.7</v>
+      </c>
       <c r="L22">
         <v>18</v>
       </c>
@@ -1327,11 +1486,23 @@
         <v>16.2</v>
       </c>
       <c r="F23">
-        <v>21.8</v>
+        <v>21.7</v>
+      </c>
+      <c r="I23">
+        <v>21.4</v>
+      </c>
+      <c r="J23">
+        <v>19.6</v>
+      </c>
+      <c r="K23">
+        <v>14.7</v>
       </c>
       <c r="L23">
         <v>18.6</v>
       </c>
+      <c r="M23">
+        <v>17.3</v>
+      </c>
       <c r="R23" s="2">
         <v>26990</v>
       </c>
@@ -1361,8 +1532,14 @@
       <c r="F24">
         <v>20.9</v>
       </c>
+      <c r="I24">
+        <v>23.3</v>
+      </c>
+      <c r="K24">
+        <v>16.6</v>
+      </c>
       <c r="L24">
-        <v>20</v>
+        <v>18.6</v>
       </c>
       <c r="R24" s="2">
         <v>26991</v>
@@ -1393,8 +1570,20 @@
       <c r="F25">
         <v>20.7</v>
       </c>
+      <c r="I25">
+        <v>22.8</v>
+      </c>
+      <c r="J25">
+        <v>20.1</v>
+      </c>
+      <c r="K25">
+        <v>15.4</v>
+      </c>
       <c r="L25">
-        <v>19.8</v>
+        <v>18.4</v>
+      </c>
+      <c r="M25">
+        <v>18.4</v>
       </c>
       <c r="R25" s="2">
         <v>26992</v>
@@ -1425,8 +1614,20 @@
       <c r="F26">
         <v>22.1</v>
       </c>
+      <c r="I26">
+        <v>26.7</v>
+      </c>
+      <c r="J26">
+        <v>20.2</v>
+      </c>
+      <c r="K26">
+        <v>14.6</v>
+      </c>
       <c r="L26">
-        <v>20.8</v>
+        <v>18.4</v>
+      </c>
+      <c r="M26">
+        <v>19.5</v>
       </c>
       <c r="R26" s="2">
         <v>26993</v>
@@ -1457,8 +1658,23 @@
       <c r="F27">
         <v>20.7</v>
       </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>18.8</v>
+      </c>
+      <c r="I27">
+        <v>23.7</v>
+      </c>
+      <c r="K27">
+        <v>17.1</v>
+      </c>
       <c r="L27">
-        <v>22.2</v>
+        <v>21.2</v>
+      </c>
+      <c r="M27">
+        <v>16.9</v>
       </c>
       <c r="R27" s="2">
         <v>26994</v>
@@ -1489,8 +1705,26 @@
       <c r="F28">
         <v>20.7</v>
       </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>17.7</v>
+      </c>
+      <c r="I28">
+        <v>22.8</v>
+      </c>
+      <c r="J28">
+        <v>20</v>
+      </c>
+      <c r="K28">
+        <v>15.8</v>
+      </c>
       <c r="L28">
-        <v>19.5</v>
+        <v>18.1</v>
+      </c>
+      <c r="M28">
+        <v>18.3</v>
       </c>
       <c r="R28" s="2">
         <v>26995</v>
@@ -1512,11 +1746,32 @@
       <c r="C29">
         <v>28</v>
       </c>
+      <c r="D29">
+        <v>27.4</v>
+      </c>
+      <c r="E29">
+        <v>15.6</v>
+      </c>
       <c r="F29">
-        <v>20.5</v>
+        <v>21.5</v>
+      </c>
+      <c r="G29">
+        <v>0.2</v>
+      </c>
+      <c r="H29">
+        <v>18</v>
+      </c>
+      <c r="I29">
+        <v>25.8</v>
+      </c>
+      <c r="K29">
+        <v>15.3</v>
       </c>
       <c r="L29">
-        <v>20.2</v>
+        <v>17.8</v>
+      </c>
+      <c r="M29">
+        <v>19.6</v>
       </c>
       <c r="R29" s="2">
         <v>26996</v>
@@ -1539,16 +1794,31 @@
         <v>29</v>
       </c>
       <c r="D30">
-        <v>28.6</v>
+        <v>28.4</v>
       </c>
       <c r="E30">
-        <v>17.3</v>
+        <v>17.1</v>
       </c>
       <c r="F30">
         <v>22.6</v>
       </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>17.7</v>
+      </c>
+      <c r="I30">
+        <v>26</v>
+      </c>
+      <c r="K30">
+        <v>15.7</v>
+      </c>
       <c r="L30">
-        <v>19.8</v>
+        <v>17.1</v>
+      </c>
+      <c r="M30">
+        <v>19.4</v>
       </c>
       <c r="R30" s="2">
         <v>26997</v>
@@ -1579,8 +1849,23 @@
       <c r="F31">
         <v>22.6</v>
       </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>18</v>
+      </c>
+      <c r="I31">
+        <v>27.1</v>
+      </c>
+      <c r="K31">
+        <v>15.7</v>
+      </c>
       <c r="L31">
-        <v>20.2</v>
+        <v>20.3</v>
+      </c>
+      <c r="M31">
+        <v>18.8</v>
       </c>
       <c r="R31" s="2">
         <v>26998</v>

--- a/results/04_final_refined_daily_hydroclimate_data/905/Daily_temperature_and_precipitation_station_905.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/905/Daily_temperature_and_precipitation_station_905.xlsx
@@ -970,7 +970,7 @@
         <v>16.6</v>
       </c>
       <c r="L11">
-        <v>19</v>
+        <v>21.4</v>
       </c>
       <c r="M11">
         <v>17.7</v>
@@ -1095,18 +1095,12 @@
       <c r="G14">
         <v>0</v>
       </c>
-      <c r="I14">
-        <v>22.8</v>
-      </c>
       <c r="J14">
         <v>20.9</v>
       </c>
       <c r="K14">
         <v>17.9</v>
       </c>
-      <c r="L14">
-        <v>20.9</v>
-      </c>
       <c r="M14">
         <v>19.9</v>
       </c>
@@ -1281,7 +1275,7 @@
         <v>16.7</v>
       </c>
       <c r="L18">
-        <v>21.6</v>
+        <v>20.8</v>
       </c>
       <c r="M18">
         <v>19.3</v>
@@ -1369,7 +1363,7 @@
         <v>15</v>
       </c>
       <c r="L20">
-        <v>16.2</v>
+        <v>17.7</v>
       </c>
       <c r="M20">
         <v>15.1</v>
@@ -1459,6 +1453,9 @@
       <c r="L22">
         <v>18</v>
       </c>
+      <c r="M22">
+        <v>16.9</v>
+      </c>
       <c r="R22" s="2">
         <v>26989</v>
       </c>
@@ -1532,15 +1529,21 @@
       <c r="F24">
         <v>20.9</v>
       </c>
+      <c r="H24">
+        <v>17.5</v>
+      </c>
       <c r="I24">
         <v>23.3</v>
       </c>
       <c r="K24">
-        <v>16.6</v>
+        <v>16.1</v>
       </c>
       <c r="L24">
         <v>18.6</v>
       </c>
+      <c r="M24">
+        <v>18.8</v>
+      </c>
       <c r="R24" s="2">
         <v>26991</v>
       </c>
@@ -1670,9 +1673,6 @@
       <c r="K27">
         <v>17.1</v>
       </c>
-      <c r="L27">
-        <v>21.2</v>
-      </c>
       <c r="M27">
         <v>16.9</v>
       </c>
@@ -1858,14 +1858,14 @@
       <c r="I31">
         <v>27.1</v>
       </c>
+      <c r="J31">
+        <v>22.2</v>
+      </c>
       <c r="K31">
         <v>15.7</v>
       </c>
-      <c r="L31">
-        <v>20.3</v>
-      </c>
       <c r="M31">
-        <v>18.8</v>
+        <v>17.3</v>
       </c>
       <c r="R31" s="2">
         <v>26998</v>

--- a/results/04_final_refined_daily_hydroclimate_data/905/Daily_temperature_and_precipitation_station_905.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/905/Daily_temperature_and_precipitation_station_905.xlsx
@@ -567,7 +567,7 @@
         <v>16.9</v>
       </c>
       <c r="F3">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="G3">
         <v>12.3</v>
@@ -1010,12 +1010,18 @@
       <c r="I12">
         <v>26.7</v>
       </c>
+      <c r="J12">
+        <v>23.1</v>
+      </c>
       <c r="K12">
         <v>16.8</v>
       </c>
       <c r="L12">
         <v>20</v>
       </c>
+      <c r="M12">
+        <v>18.2</v>
+      </c>
       <c r="R12" s="2">
         <v>26979</v>
       </c>
@@ -1095,12 +1101,18 @@
       <c r="G14">
         <v>0</v>
       </c>
+      <c r="I14">
+        <v>22.8</v>
+      </c>
       <c r="J14">
         <v>20.9</v>
       </c>
       <c r="K14">
         <v>17.9</v>
       </c>
+      <c r="L14">
+        <v>20.9</v>
+      </c>
       <c r="M14">
         <v>19.9</v>
       </c>
@@ -1363,7 +1375,7 @@
         <v>15</v>
       </c>
       <c r="L20">
-        <v>17.7</v>
+        <v>16.2</v>
       </c>
       <c r="M20">
         <v>15.1</v>
@@ -1529,14 +1541,11 @@
       <c r="F24">
         <v>20.9</v>
       </c>
-      <c r="H24">
-        <v>17.5</v>
-      </c>
       <c r="I24">
         <v>23.3</v>
       </c>
       <c r="K24">
-        <v>16.1</v>
+        <v>16.6</v>
       </c>
       <c r="L24">
         <v>18.6</v>
@@ -1620,9 +1629,6 @@
       <c r="I26">
         <v>26.7</v>
       </c>
-      <c r="J26">
-        <v>20.2</v>
-      </c>
       <c r="K26">
         <v>14.6</v>
       </c>
@@ -1630,7 +1636,7 @@
         <v>18.4</v>
       </c>
       <c r="M26">
-        <v>19.5</v>
+        <v>18.7</v>
       </c>
       <c r="R26" s="2">
         <v>26993</v>

--- a/results/04_final_refined_daily_hydroclimate_data/905/Daily_temperature_and_precipitation_station_905.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/905/Daily_temperature_and_precipitation_station_905.xlsx
@@ -585,7 +585,7 @@
         <v>17.6</v>
       </c>
       <c r="L3">
-        <v>20</v>
+        <v>21.3</v>
       </c>
       <c r="M3">
         <v>17.2</v>
@@ -635,7 +635,7 @@
         <v>16.4</v>
       </c>
       <c r="L4">
-        <v>20.6</v>
+        <v>22.3</v>
       </c>
       <c r="M4">
         <v>19.2</v>
@@ -685,7 +685,7 @@
         <v>17.9</v>
       </c>
       <c r="L5">
-        <v>21</v>
+        <v>22.7</v>
       </c>
       <c r="M5">
         <v>19.6</v>
@@ -735,7 +735,7 @@
         <v>15.8</v>
       </c>
       <c r="L6">
-        <v>22.2</v>
+        <v>22.8</v>
       </c>
       <c r="M6">
         <v>18</v>
@@ -782,10 +782,10 @@
         <v>17</v>
       </c>
       <c r="L7">
-        <v>19.7</v>
+        <v>21.5</v>
       </c>
       <c r="M7">
-        <v>19</v>
+        <v>19.8</v>
       </c>
       <c r="R7" s="2">
         <v>26974</v>
@@ -832,7 +832,7 @@
         <v>19.5</v>
       </c>
       <c r="M8">
-        <v>19.7</v>
+        <v>20.2</v>
       </c>
       <c r="R8" s="2">
         <v>26975</v>
@@ -923,7 +923,7 @@
         <v>17.2</v>
       </c>
       <c r="L10">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="M10">
         <v>19.4</v>
@@ -973,7 +973,7 @@
         <v>21.4</v>
       </c>
       <c r="M11">
-        <v>17.7</v>
+        <v>18.1</v>
       </c>
       <c r="R11" s="2">
         <v>26978</v>
@@ -1016,9 +1016,6 @@
       <c r="K12">
         <v>16.8</v>
       </c>
-      <c r="L12">
-        <v>20</v>
-      </c>
       <c r="M12">
         <v>18.2</v>
       </c>
@@ -1054,6 +1051,9 @@
       <c r="G13">
         <v>2.3</v>
       </c>
+      <c r="H13">
+        <v>18</v>
+      </c>
       <c r="I13">
         <v>23.8</v>
       </c>
@@ -1063,11 +1063,8 @@
       <c r="K13">
         <v>17.4</v>
       </c>
-      <c r="L13">
-        <v>18.7</v>
-      </c>
       <c r="M13">
-        <v>18.4</v>
+        <v>19.9</v>
       </c>
       <c r="R13" s="2">
         <v>26980</v>
@@ -1111,10 +1108,10 @@
         <v>17.9</v>
       </c>
       <c r="L14">
-        <v>20.9</v>
+        <v>21.4</v>
       </c>
       <c r="M14">
-        <v>19.9</v>
+        <v>20.2</v>
       </c>
       <c r="R14" s="2">
         <v>26981</v>
@@ -1189,6 +1186,9 @@
       <c r="G16">
         <v>0</v>
       </c>
+      <c r="H16">
+        <v>18</v>
+      </c>
       <c r="I16">
         <v>25.1</v>
       </c>
@@ -1198,11 +1198,8 @@
       <c r="K16">
         <v>17.7</v>
       </c>
-      <c r="L16">
-        <v>20.2</v>
-      </c>
       <c r="M16">
-        <v>17.2</v>
+        <v>19</v>
       </c>
       <c r="R16" s="2">
         <v>26983</v>
@@ -1243,7 +1240,7 @@
         <v>18.2</v>
       </c>
       <c r="L17">
-        <v>19.1</v>
+        <v>20</v>
       </c>
       <c r="R17" s="2">
         <v>26984</v>
@@ -1287,10 +1284,10 @@
         <v>16.7</v>
       </c>
       <c r="L18">
-        <v>20.8</v>
+        <v>21.6</v>
       </c>
       <c r="M18">
-        <v>19.3</v>
+        <v>19.7</v>
       </c>
       <c r="R18" s="2">
         <v>26985</v>
@@ -1331,7 +1328,7 @@
         <v>16.1</v>
       </c>
       <c r="L19">
-        <v>19.5</v>
+        <v>21.2</v>
       </c>
       <c r="R19" s="2">
         <v>26986</v>
@@ -1375,10 +1372,10 @@
         <v>15</v>
       </c>
       <c r="L20">
-        <v>16.2</v>
+        <v>17.7</v>
       </c>
       <c r="M20">
-        <v>15.1</v>
+        <v>16.4</v>
       </c>
       <c r="R20" s="2">
         <v>26987</v>
@@ -1425,7 +1422,7 @@
         <v>19.7</v>
       </c>
       <c r="M21">
-        <v>18.2</v>
+        <v>18.8</v>
       </c>
       <c r="R21" s="2">
         <v>26988</v>
@@ -1510,7 +1507,7 @@
         <v>18.6</v>
       </c>
       <c r="M23">
-        <v>17.3</v>
+        <v>18</v>
       </c>
       <c r="R23" s="2">
         <v>26990</v>
@@ -1548,7 +1545,7 @@
         <v>16.6</v>
       </c>
       <c r="L24">
-        <v>18.6</v>
+        <v>20</v>
       </c>
       <c r="M24">
         <v>18.8</v>
@@ -1592,10 +1589,10 @@
         <v>15.4</v>
       </c>
       <c r="L25">
-        <v>18.4</v>
+        <v>19.7</v>
       </c>
       <c r="M25">
-        <v>18.4</v>
+        <v>18.9</v>
       </c>
       <c r="R25" s="2">
         <v>26992</v>
@@ -1633,7 +1630,7 @@
         <v>14.6</v>
       </c>
       <c r="L26">
-        <v>18.4</v>
+        <v>20.8</v>
       </c>
       <c r="M26">
         <v>18.7</v>
@@ -1726,11 +1723,8 @@
       <c r="K28">
         <v>15.8</v>
       </c>
-      <c r="L28">
-        <v>18.1</v>
-      </c>
       <c r="M28">
-        <v>18.3</v>
+        <v>18.8</v>
       </c>
       <c r="R28" s="2">
         <v>26995</v>
@@ -1773,9 +1767,6 @@
       <c r="K29">
         <v>15.3</v>
       </c>
-      <c r="L29">
-        <v>17.8</v>
-      </c>
       <c r="M29">
         <v>19.6</v>
       </c>
@@ -1820,9 +1811,6 @@
       <c r="K30">
         <v>15.7</v>
       </c>
-      <c r="L30">
-        <v>17.1</v>
-      </c>
       <c r="M30">
         <v>19.4</v>
       </c>
@@ -1870,8 +1858,11 @@
       <c r="K31">
         <v>15.7</v>
       </c>
+      <c r="L31">
+        <v>20.3</v>
+      </c>
       <c r="M31">
-        <v>17.3</v>
+        <v>18.8</v>
       </c>
       <c r="R31" s="2">
         <v>26998</v>
